--- a/artfynd/A 60322-2025 artfynd.xlsx
+++ b/artfynd/A 60322-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128502885</v>
       </c>
       <c r="B2" t="n">
-        <v>58093</v>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60322-2025 artfynd.xlsx
+++ b/artfynd/A 60322-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,8 +800,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128502885</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 60322-2025 artfynd.xlsx
+++ b/artfynd/A 60322-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128502885</v>
+        <v>136251639</v>
       </c>
       <c r="B2" t="n">
-        <v>58327</v>
+        <v>57979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,36 +708,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skarpudden, Hls</t>
+          <t>Bastnäs, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600143</v>
+        <v>600210</v>
       </c>
       <c r="R2" t="n">
-        <v>6781692</v>
+        <v>6781740</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,22 +753,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,13 +784,255 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136251639</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128502885</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skarpudden, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>600143</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6781692</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/128502885</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136251579</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8452</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bastnäs, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>600079</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6781634</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136251579</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60322-2025 artfynd.xlsx
+++ b/artfynd/A 60322-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136251639</v>
       </c>
       <c r="B2" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60322-2025 artfynd.xlsx
+++ b/artfynd/A 60322-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136251639</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60322-2025 artfynd.xlsx
+++ b/artfynd/A 60322-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136251639</v>
       </c>
       <c r="B2" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60322-2025 artfynd.xlsx
+++ b/artfynd/A 60322-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136251639</v>
       </c>
       <c r="B2" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60322-2025 artfynd.xlsx
+++ b/artfynd/A 60322-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136251639</v>
       </c>
       <c r="B2" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
